--- a/data/Departamento_de_correccion_y_rehabilitacion/dcr_PEA.xlsx
+++ b/data/Departamento_de_correccion_y_rehabilitacion/dcr_PEA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Departamento_de_correccion_y_rehabilitacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89137E3-E4BC-436D-9378-6302A51F717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8FC001-E9BA-4078-9448-39573A43428C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resumen_activos" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="32">
   <si>
     <t>Tipo de delito</t>
   </si>
@@ -199,12 +199,15 @@
   <si>
     <t>Región</t>
   </si>
+  <si>
+    <t>2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,6 +236,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -242,7 +251,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -250,11 +259,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -265,6 +289,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,14 +573,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -569,8 +596,11 @@
       <c r="E1" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -586,8 +616,11 @@
       <c r="E2">
         <v>1104</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="5">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -603,8 +636,11 @@
       <c r="E3">
         <v>708</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="5">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -620,8 +656,11 @@
       <c r="E4">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="5">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -637,8 +676,11 @@
       <c r="E5">
         <v>208</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="5">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -658,8 +700,13 @@
         <f>SUM(E2:E5)</f>
         <v>2116</v>
       </c>
+      <c r="F6">
+        <f>SUM(F2:F5)</f>
+        <v>2063</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="B6" formulaRange="1"/>
